--- a/artfynd/A 5048-2025 artfynd.xlsx
+++ b/artfynd/A 5048-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126135163</v>
       </c>
       <c r="B2" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -758,6 +758,16 @@
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>Maria Östlin</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Maria Östlin</t>
+        </is>
+      </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -765,7 +775,7 @@
         <v>126135181</v>
       </c>
       <c r="B3" t="n">
-        <v>98257</v>
+        <v>98259</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -845,6 +855,16 @@
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Maria Östlin</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Maria Östlin</t>
+        </is>
+      </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -852,7 +872,7 @@
         <v>126135152</v>
       </c>
       <c r="B4" t="n">
-        <v>98245</v>
+        <v>98247</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -932,6 +952,16 @@
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Maria Östlin</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Maria Östlin</t>
+        </is>
+      </c>
       <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>

--- a/artfynd/A 5048-2025 artfynd.xlsx
+++ b/artfynd/A 5048-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126135163</v>
+        <v>126135181</v>
       </c>
       <c r="B2" t="n">
-        <v>98364</v>
+        <v>98259</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545582</v>
+        <v>545581</v>
       </c>
       <c r="R2" t="n">
-        <v>7016693</v>
+        <v>7016763</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126135181</v>
+        <v>126135163</v>
       </c>
       <c r="B3" t="n">
-        <v>98259</v>
+        <v>98364</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545581</v>
+        <v>545582</v>
       </c>
       <c r="R3" t="n">
-        <v>7016763</v>
+        <v>7016693</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>

--- a/artfynd/A 5048-2025 artfynd.xlsx
+++ b/artfynd/A 5048-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126135181</v>
+        <v>126135163</v>
       </c>
       <c r="B2" t="n">
-        <v>98259</v>
+        <v>98366</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545581</v>
+        <v>545582</v>
       </c>
       <c r="R2" t="n">
-        <v>7016763</v>
+        <v>7016693</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126135163</v>
+        <v>126135181</v>
       </c>
       <c r="B3" t="n">
-        <v>98364</v>
+        <v>98261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545582</v>
+        <v>545581</v>
       </c>
       <c r="R3" t="n">
-        <v>7016693</v>
+        <v>7016763</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -872,7 +872,7 @@
         <v>126135152</v>
       </c>
       <c r="B4" t="n">
-        <v>98247</v>
+        <v>98249</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5048-2025 artfynd.xlsx
+++ b/artfynd/A 5048-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126135163</v>
+        <v>126135181</v>
       </c>
       <c r="B2" t="n">
-        <v>98366</v>
+        <v>98261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545582</v>
+        <v>545581</v>
       </c>
       <c r="R2" t="n">
-        <v>7016693</v>
+        <v>7016763</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126135181</v>
+        <v>126135163</v>
       </c>
       <c r="B3" t="n">
-        <v>98261</v>
+        <v>98366</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545581</v>
+        <v>545582</v>
       </c>
       <c r="R3" t="n">
-        <v>7016763</v>
+        <v>7016693</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>

--- a/artfynd/A 5048-2025 artfynd.xlsx
+++ b/artfynd/A 5048-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126135181</v>
+        <v>126135163</v>
       </c>
       <c r="B2" t="n">
-        <v>98261</v>
+        <v>98368</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545581</v>
+        <v>545582</v>
       </c>
       <c r="R2" t="n">
-        <v>7016763</v>
+        <v>7016693</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126135163</v>
+        <v>126135181</v>
       </c>
       <c r="B3" t="n">
-        <v>98366</v>
+        <v>98263</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545582</v>
+        <v>545581</v>
       </c>
       <c r="R3" t="n">
-        <v>7016693</v>
+        <v>7016763</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -872,7 +872,7 @@
         <v>126135152</v>
       </c>
       <c r="B4" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5048-2025 artfynd.xlsx
+++ b/artfynd/A 5048-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126135163</v>
       </c>
       <c r="B2" t="n">
-        <v>98368</v>
+        <v>98372</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126135181</v>
       </c>
       <c r="B3" t="n">
-        <v>98263</v>
+        <v>98267</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126135152</v>
       </c>
       <c r="B4" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5048-2025 artfynd.xlsx
+++ b/artfynd/A 5048-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126135163</v>
       </c>
       <c r="B2" t="n">
-        <v>98372</v>
+        <v>98375</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126135181</v>
       </c>
       <c r="B3" t="n">
-        <v>98267</v>
+        <v>98270</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126135152</v>
       </c>
       <c r="B4" t="n">
-        <v>98255</v>
+        <v>98258</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5048-2025 artfynd.xlsx
+++ b/artfynd/A 5048-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126135163</v>
       </c>
       <c r="B2" t="n">
-        <v>98375</v>
+        <v>98384</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126135181</v>
       </c>
       <c r="B3" t="n">
-        <v>98270</v>
+        <v>98279</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126135152</v>
       </c>
       <c r="B4" t="n">
-        <v>98258</v>
+        <v>98267</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5048-2025 artfynd.xlsx
+++ b/artfynd/A 5048-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126135163</v>
+        <v>126135152</v>
       </c>
       <c r="B2" t="n">
-        <v>98384</v>
+        <v>99024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219847</v>
+        <v>504</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126135181</v>
+        <v>126135163</v>
       </c>
       <c r="B3" t="n">
-        <v>98279</v>
+        <v>99142</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545581</v>
+        <v>545582</v>
       </c>
       <c r="R3" t="n">
-        <v>7016763</v>
+        <v>7016693</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126135152</v>
+        <v>126135181</v>
       </c>
       <c r="B4" t="n">
-        <v>98267</v>
+        <v>99036</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>504</v>
+        <v>223591</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545582</v>
+        <v>545581</v>
       </c>
       <c r="R4" t="n">
-        <v>7016693</v>
+        <v>7016763</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>

--- a/artfynd/A 5048-2025 artfynd.xlsx
+++ b/artfynd/A 5048-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126135152</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126135163</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,8 +978,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126135181</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>